--- a/product_upload/packages/63/file.xlsx
+++ b/product_upload/packages/63/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -832,6 +837,11 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>HYMOX 125MG-5ML POWDER FOR ORAL SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-21FD356EDE76</t>
         </is>
       </c>
@@ -855,7 +865,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1010,6 +1020,11 @@
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>HYLO-COMOD 0.1% EYE DROP</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-5529A8776B0C</t>
         </is>
       </c>
@@ -1033,7 +1048,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1192,6 +1207,11 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>HYMOX 250MG-5ML POWDER FOR ORAL SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-896370D1B0D9</t>
         </is>
       </c>
@@ -1215,7 +1235,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1376,6 +1396,11 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>HYZAAR 50/12.5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-0E2108AECF7C</t>
         </is>
       </c>
@@ -1399,7 +1424,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1558,6 +1583,11 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>HYPOSEC 20 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-93ED4BA9CFC5</t>
         </is>
       </c>
@@ -1581,7 +1611,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1740,6 +1770,11 @@
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>DIFFERIN 0.1% GEL</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-5A50A5C1A5F3</t>
         </is>
       </c>
@@ -1763,7 +1798,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1926,6 +1961,11 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>DIFFERIN 0.1% CREAM</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-B77A4A2A9061</t>
         </is>
       </c>
@@ -1949,7 +1989,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2104,6 +2144,11 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>DICLOGESIC</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-30C64ACE34DC</t>
         </is>
       </c>
@@ -2127,7 +2172,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2282,6 +2327,11 @@
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>DURACAN 150MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-7648F4EA62DD</t>
         </is>
       </c>
@@ -2305,7 +2355,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2460,6 +2510,11 @@
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>DOXYCIN</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-B71FA909429D</t>
         </is>
       </c>
@@ -2483,7 +2538,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2634,6 +2689,11 @@
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>FERRIPROX 100MG/ML ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-CD139B18C944</t>
         </is>
       </c>
@@ -2657,7 +2717,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2812,6 +2872,11 @@
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>FENAM 50MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-0D6C84D602DA</t>
         </is>
       </c>
@@ -2835,7 +2900,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2990,6 +3055,11 @@
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>FLUDREX SYRUP</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-6B1F6B030B03</t>
         </is>
       </c>
@@ -3013,7 +3083,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3170,6 +3240,11 @@
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>ENTAPRO 20MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-5071C2F349FD</t>
         </is>
       </c>
@@ -3193,7 +3268,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3346,6 +3421,11 @@
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>ENTAPRO 10MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-C87AD48DE3AD</t>
         </is>
       </c>
@@ -3369,7 +3449,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3524,6 +3604,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>ENEMACORT 0.02MG-ML TABLET FOR ENEMA</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-6ED3C4B092F6</t>
         </is>
       </c>
@@ -3547,7 +3632,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3706,6 +3791,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>ELIDEL 1% CREAM</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-EBD71FCF0216</t>
         </is>
       </c>
@@ -3729,7 +3819,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3896,6 +3986,11 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>EMIDOL 500MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-C9C580948676</t>
         </is>
       </c>
@@ -3919,7 +4014,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4082,6 +4177,11 @@
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>EMILOK 20MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-8DEC04E6447C</t>
         </is>
       </c>
@@ -4105,7 +4205,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4264,6 +4364,11 @@
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>EZOLVIN 8MGTAB</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-DED5C7EB1281</t>
         </is>
       </c>
@@ -4287,7 +4392,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4446,6 +4551,11 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>EZILAX 10G-15ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-58223C66927E</t>
         </is>
       </c>
@@ -4469,7 +4579,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4624,6 +4734,11 @@
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>ARXIA 60MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-ED9859E272D2</t>
         </is>
       </c>
@@ -4647,7 +4762,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4802,6 +4917,11 @@
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>ARXIA 120MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-2BAB21E5F9CB</t>
         </is>
       </c>
@@ -4825,7 +4945,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4980,6 +5100,11 @@
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>ROXARDIO 20MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-C9F92C1ED7A4</t>
         </is>
       </c>
@@ -5003,7 +5128,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5166,6 +5291,11 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>ROXARDIO 10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-05E4ACF5D343</t>
         </is>
       </c>
@@ -5189,7 +5319,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5344,6 +5474,11 @@
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>VERCANZA 450 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-0D3A4D67B336</t>
         </is>
       </c>
@@ -5367,7 +5502,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5530,6 +5665,11 @@
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>Fostimon 300 I.U</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-003BE1681889</t>
         </is>
       </c>
@@ -5553,7 +5693,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5714,6 +5854,11 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>SENERGY 10 MG/160 MG F.C. TABLET</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-4BEDEDC3CCB5</t>
         </is>
       </c>
@@ -5737,7 +5882,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5898,6 +6043,11 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>SENERGY 5 MG/160 MG F.C. TABLET</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-8073B273E132</t>
         </is>
       </c>
@@ -5921,7 +6071,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6080,6 +6230,11 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>GLERAN 15MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-A73D502DA47F</t>
         </is>
       </c>
@@ -6103,7 +6258,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6258,6 +6413,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>GLERAN 30MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-BA5B6909129C</t>
         </is>
       </c>
@@ -6281,7 +6441,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6444,6 +6604,11 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>OROTIX 90MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-1C007E8A1410</t>
         </is>
       </c>
@@ -6467,7 +6632,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6626,6 +6791,11 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>JULMENTIN FORTE 312.5MG POWDER FOR SUSP</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-A54C429D120B</t>
         </is>
       </c>
@@ -6649,7 +6819,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -6800,6 +6970,11 @@
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>JULMENTIN 2X. 457MG-5ML ORAL SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-97CC2DA6E92E</t>
         </is>
       </c>
@@ -6823,7 +6998,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -6978,6 +7153,11 @@
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>DICLOGESIC RETARD</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-97F0185368FA</t>
         </is>
       </c>
@@ -7001,7 +7181,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7160,6 +7340,11 @@
       </c>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>DURADOX 100 MG CAPS</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-4732B82790F1</t>
         </is>
       </c>
@@ -7183,7 +7368,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7342,6 +7527,11 @@
       </c>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>CLAMYCIN 500 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-009D46D58973</t>
         </is>
       </c>
@@ -7365,7 +7555,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7528,6 +7718,11 @@
       </c>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>CLOFEN CREAMAGEL 1%</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-C453C7852A10</t>
         </is>
       </c>
@@ -7551,7 +7746,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7710,6 +7905,11 @@
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>FUSIX 40MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-8EFA3F038244</t>
         </is>
       </c>
@@ -7733,7 +7933,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -7892,6 +8092,11 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>CHLOROHISTOL TAB 4 MG.</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-F2572B734107</t>
         </is>
       </c>
@@ -7915,7 +8120,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8074,6 +8279,11 @@
       </c>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>SOOLAN SYRUP 100 ML.</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-B50315C66BB8</t>
         </is>
       </c>
@@ -8097,7 +8307,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8252,6 +8462,11 @@
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>ARXIA 90MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-549EBDC786F6</t>
         </is>
       </c>
@@ -8275,7 +8490,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8430,6 +8645,11 @@
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>AMLOPHAR 5MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-08D78D3E7FA8</t>
         </is>
       </c>
@@ -8453,7 +8673,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8604,6 +8824,11 @@
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>3V TABLETS</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-42FF4AB6A89E</t>
         </is>
       </c>
@@ -8627,7 +8852,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -8786,6 +9011,11 @@
       </c>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>BEPANTHEN</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-EDD72B204841</t>
         </is>
       </c>
@@ -8809,7 +9039,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -8964,6 +9194,11 @@
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>ALOPEXY 5% topical solution</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-0ACEBEB6A935</t>
         </is>
       </c>
@@ -8987,7 +9222,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9146,6 +9381,11 @@
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>ALOPEXY 5% topical solution</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-FF084D1E3D0C</t>
         </is>
       </c>
@@ -9169,7 +9409,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9328,6 +9568,11 @@
       </c>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>TYKERB 250MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-75C3FA3322DB</t>
         </is>
       </c>
@@ -9351,7 +9596,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9510,6 +9755,11 @@
       </c>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>KEPPRA 1000MG F.C.TAB</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-BA00EB1F553D</t>
         </is>
       </c>
@@ -9533,7 +9783,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -9690,6 +9940,11 @@
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>KEPPRA 100MG-ML ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-9954B09E6C0D</t>
         </is>
       </c>
@@ -9713,7 +9968,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -9872,6 +10127,11 @@
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>PROTOPIC 0.03% OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-95B9C76BB2D6</t>
         </is>
       </c>
@@ -9895,7 +10155,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10056,6 +10316,11 @@
       </c>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>KEPPRA 250MG F.C.TAB</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-C5074A0BC2B8</t>
         </is>
       </c>
@@ -10079,7 +10344,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10232,6 +10497,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>KEPPRA 500MG F.C.TAB</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-907157217E90</t>
         </is>
       </c>
@@ -10255,7 +10525,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10410,6 +10680,11 @@
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>ACUVAIL ophthalmic solution</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-9F9F0DEE33D7</t>
         </is>
       </c>
@@ -10433,7 +10708,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10588,6 +10863,11 @@
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>AVOQUIN cream</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-4BED77F377CC</t>
         </is>
       </c>
@@ -10611,7 +10891,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -10770,6 +11050,11 @@
       </c>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>BRONCAST 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-04BAE82D55E8</t>
         </is>
       </c>
@@ -10793,7 +11078,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -10952,6 +11237,11 @@
       </c>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>BRONCAST 5 mg chewable tablet</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-866C94DC5902</t>
         </is>
       </c>
@@ -10975,7 +11265,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11130,6 +11420,11 @@
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>ZYMAXID 0.5% eye drops solution</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-B1419700D440</t>
         </is>
       </c>
@@ -11153,7 +11448,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11314,6 +11609,11 @@
       </c>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>CATAFLAM 50MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-CD8C76615A6D</t>
         </is>
       </c>
@@ -11337,7 +11637,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11492,6 +11792,11 @@
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>LESCOL XL 80 MG FILM COATED TAB</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-C7018923099D</t>
         </is>
       </c>
@@ -11515,7 +11820,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -11672,6 +11977,11 @@
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>DEPAKINE 57.64MG-ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-6E191B2CB202</t>
         </is>
       </c>
@@ -11695,7 +12005,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -11854,6 +12164,11 @@
       </c>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>VIRECTIL 50 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-F0608124C9BB</t>
         </is>
       </c>
@@ -11877,7 +12192,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12032,6 +12347,11 @@
       </c>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>KEMADRIN 5MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-2D2B45D30620</t>
         </is>
       </c>
@@ -12055,7 +12375,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12210,6 +12530,11 @@
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>AKYNZEO 300 mg/0.5 mg hard capsules</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-DB205B5BE0FD</t>
         </is>
       </c>
@@ -12233,7 +12558,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12388,6 +12713,11 @@
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>AZYN 500 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-FCB61900BC35</t>
         </is>
       </c>
@@ -12411,7 +12741,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -12574,6 +12904,11 @@
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>ULTRA-FUSION Ophthalmic Solution</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-18669A30A09B</t>
         </is>
       </c>
@@ -12597,7 +12932,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -12756,6 +13091,11 @@
       </c>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>ORGALUTRAN 0.25MG\0.5ML SYRINGE</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-434DB1D44714</t>
         </is>
       </c>
@@ -12779,7 +13119,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -12938,6 +13278,11 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>PANADOL COLD &amp; FLU VAPOUR RELEASE + DECONGESTANT  600 MG ORAL S</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-E5307FEB4919</t>
         </is>
       </c>
@@ -12961,7 +13306,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13124,6 +13469,11 @@
       </c>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>HEMLIBRA 150 MG/ML SOLUTION FOR INJECTION</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-F703C09E04D2</t>
         </is>
       </c>
@@ -13147,7 +13497,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13306,6 +13656,11 @@
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>HEMLIBRA 150 MG/ML SOLUTION FOR INJECTION</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-6321A9267B3C</t>
         </is>
       </c>
@@ -13329,7 +13684,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -13488,6 +13843,11 @@
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>HEMLIBRA 150 MG/ML SOLUTION FOR INJECTION</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-999DF5A4002C</t>
         </is>
       </c>
@@ -13511,7 +13871,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -13674,6 +14034,11 @@
       </c>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>HEMLIBRA 30 MG/ML SOLUTION FOR INJECTION</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-4079121F46D0</t>
         </is>
       </c>
@@ -13697,7 +14062,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -13852,6 +14217,11 @@
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>ARCOXIA 60MG TAB</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-EE9245767284</t>
         </is>
       </c>
@@ -13875,7 +14245,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14030,6 +14400,11 @@
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>ARCOXIA 90MG TAB</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-472BA4A4B5CA</t>
         </is>
       </c>
@@ -14053,7 +14428,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14212,6 +14587,11 @@
       </c>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>CARPAZIO 600 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-53F5D7F243B5</t>
         </is>
       </c>
@@ -14235,7 +14615,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14394,6 +14774,11 @@
       </c>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>Arkator 60MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-857E856AB416</t>
         </is>
       </c>
@@ -14417,7 +14802,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -14572,6 +14957,11 @@
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>Arkator 90MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-BE97ABCEC2F3</t>
         </is>
       </c>
@@ -14595,7 +14985,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -14750,6 +15140,11 @@
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>Arkator 120MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-5966BCCF6D2B</t>
         </is>
       </c>
@@ -14773,7 +15168,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -14932,6 +15327,11 @@
       </c>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>PLATEREL 5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-8ADE068AF470</t>
         </is>
       </c>
@@ -14955,7 +15355,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15114,6 +15514,11 @@
       </c>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>PLATEREL 10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-717E1B786237</t>
         </is>
       </c>
@@ -15137,7 +15542,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15296,6 +15701,11 @@
       </c>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>ZAHRA TABLET</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-8E9ED4817EDA</t>
         </is>
       </c>
@@ -15319,7 +15729,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -15474,6 +15884,11 @@
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>MONTAS 4 mg Chewable Tablets</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-78B9662BF803</t>
         </is>
       </c>
@@ -15497,7 +15912,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -15652,6 +16067,11 @@
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>MONTAS 5 mg Chewable Tablets</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-B2426C449644</t>
         </is>
       </c>
@@ -15675,7 +16095,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -15834,6 +16254,11 @@
       </c>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>ZYTERO 12.5 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-28F14EBEE798</t>
         </is>
       </c>
@@ -15857,7 +16282,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16012,6 +16437,11 @@
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>ZYTERO 25 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-958D95ABCF1C</t>
         </is>
       </c>
@@ -16035,7 +16465,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16190,6 +16620,11 @@
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>OXIRA 8MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-4929DE80ED75</t>
         </is>
       </c>
@@ -16213,7 +16648,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16372,6 +16807,11 @@
       </c>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>MARLET 2.5 MG F.C. TABLET</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-D85AA5F2CB68</t>
         </is>
       </c>
@@ -16395,7 +16835,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -16554,6 +16994,11 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>ALDACTONE TAB</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-6CC5737CEE2C</t>
         </is>
       </c>
@@ -16577,7 +17022,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -16738,6 +17183,11 @@
       </c>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>ZYLORIC 100MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-F2612A33DBBD</t>
         </is>
       </c>
@@ -16761,7 +17211,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -16916,6 +17366,11 @@
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>MAXITROL</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-1D985C25AC14</t>
         </is>
       </c>
@@ -16939,7 +17394,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17102,6 +17557,11 @@
       </c>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>SALAZOPYRIN-EN TAB 500MG</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-8D25187CDF87</t>
         </is>
       </c>
@@ -17125,7 +17585,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17284,6 +17744,11 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>LIVADOR 750MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-6C20078CEB8D</t>
         </is>
       </c>
@@ -17307,7 +17772,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -17466,6 +17931,11 @@
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>ENNLA 5% Cream</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-FCCDD07C5E58</t>
         </is>
       </c>
@@ -17489,7 +17959,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -17648,6 +18118,11 @@
       </c>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>TRELEGY ELLIPTA 100/62.5/25MCG Inhalation powder, pre-dispensed</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-E2B5042A89D8</t>
         </is>
       </c>
@@ -17671,7 +18146,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -17826,6 +18301,11 @@
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>GAMCET 0.4MG PROLONGED RELEASE F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-2373AF6D6BAC</t>
         </is>
       </c>
@@ -17849,7 +18329,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18000,6 +18480,11 @@
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>LIVADOR 500 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-056E75D10F10</t>
         </is>
       </c>
@@ -18023,7 +18508,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18182,6 +18667,11 @@
       </c>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>Xevaneer 300 mg capsule</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-09E42A25FF2C</t>
         </is>
       </c>
@@ -18205,7 +18695,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -18356,6 +18846,11 @@
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>XEVANEER 125mg/5ml Powder For Oral Suspension</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-31FB5EAEB8D6</t>
         </is>
       </c>
@@ -18379,7 +18874,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -18538,6 +19033,11 @@
       </c>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>WELLBUTRIN XL 150 EXTENDED RELEASE F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-07DD701D6A73</t>
         </is>
       </c>
@@ -18561,7 +19061,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -18719,6 +19219,11 @@
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>DESCOVY 200MG/25MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-8A6CD7B20DA2</t>
         </is>
@@ -18735,7 +19240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18781,100 +19286,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -18906,7 +19416,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -18921,92 +19431,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-28256</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>263.91</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>641</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19038,7 +19553,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19053,92 +19568,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-75873</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>300.95</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>642</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19170,7 +19690,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19185,92 +19705,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-19169</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>417.07</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>643</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19302,7 +19827,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -19317,92 +19842,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-28638</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>92.81999999999999</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>644</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19434,7 +19964,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -19449,92 +19979,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-51969</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>247.22</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>645</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19566,7 +20101,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -19581,92 +20116,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-60181</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>237.62</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>646</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19698,7 +20238,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -19713,92 +20253,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-32820</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>243.37</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>647</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19830,7 +20375,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -19845,92 +20390,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-45888</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>46.15</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>648</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19962,7 +20512,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -19977,92 +20527,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-57523</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>414.24</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>649</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20094,7 +20649,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20109,92 +20664,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-68817</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>341.89</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>650</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20226,7 +20786,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20241,92 +20801,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-86648</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>333.05</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>651</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20343,7 +20908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20449,6 +21014,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -20484,7 +21059,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -20549,6 +21124,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-A3C1CA424BF6</t>
         </is>
@@ -20585,7 +21170,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -20650,6 +21235,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-BDE142D751B0</t>
         </is>
@@ -20686,7 +21281,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -20751,6 +21346,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-8E5708240C03</t>
         </is>
@@ -20787,7 +21392,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -20852,6 +21457,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-8AAB06A15BDD</t>
         </is>
@@ -20888,7 +21503,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -20953,6 +21568,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-E88C87B53CAD</t>
         </is>
@@ -20989,7 +21614,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21054,6 +21679,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-6AD9719DF639</t>
         </is>
@@ -21090,7 +21725,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21155,6 +21790,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-085CCACE540D</t>
         </is>
@@ -21191,7 +21836,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -21256,6 +21901,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-74F8B570D4C7</t>
         </is>
@@ -21292,7 +21947,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -21357,6 +22012,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-418C2499FB3C</t>
         </is>
@@ -21393,7 +22058,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -21458,6 +22123,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-44C6E95AD56F</t>
         </is>
@@ -21494,7 +22169,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -21559,6 +22234,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-B37551A70701</t>
         </is>
@@ -21595,7 +22280,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -21660,6 +22345,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-F7DB23981B87</t>
         </is>
@@ -21696,7 +22391,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -21761,6 +22456,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-FB0EB12F438D</t>
         </is>
@@ -21797,7 +22502,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -21862,6 +22567,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-65B6EBCAC1BA</t>
         </is>
@@ -21898,7 +22613,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -21963,6 +22678,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-D92D67ED716A</t>
         </is>
@@ -21999,7 +22724,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22064,6 +22789,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-9686B665F795</t>
         </is>
@@ -22100,7 +22835,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22165,6 +22900,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-265B780FEAEE</t>
         </is>
@@ -22201,7 +22946,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -22266,6 +23011,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-CD82054B1359</t>
         </is>
@@ -22302,7 +23057,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -22367,6 +23122,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-CC43076894E6</t>
         </is>
@@ -22403,7 +23168,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -22468,6 +23233,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-57502B855315</t>
         </is>

--- a/product_upload/packages/63/file.xlsx
+++ b/product_upload/packages/63/file.xlsx
@@ -686,8 +686,16 @@
           <t>4433207507-105-623436047194</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HYMOX 125MG-5ML POWDER FOR ORAL SUSPENSION</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>HYMOX 125MG-5ML POWDER FOR ORAL SUSPENSION detailed description.</t>
+        </is>
+      </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
@@ -873,8 +881,16 @@
           <t>0039799763-996-987891034051</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HYLO-COMOD 0.1% EYE DROP</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>HYLO-COMOD 0.1% EYE DROP detailed description.</t>
+        </is>
+      </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
@@ -1056,8 +1072,16 @@
           <t>8371610714-243-123489199982</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HYMOX 250MG-5ML POWDER FOR ORAL SUSPENSION</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>HYMOX 250MG-5ML POWDER FOR ORAL SUSPENSION detailed description.</t>
+        </is>
+      </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
@@ -1243,8 +1267,16 @@
           <t>4938449753-306-724275387358</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HYZAAR 50/12.5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>HYZAAR 50/12.5 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>Pharma Pharmaceutical Industries (PPI)</t>
@@ -1432,8 +1464,16 @@
           <t>4442798563-840-494317652628</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HYPOSEC 20 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>HYPOSEC 20 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
@@ -1619,8 +1659,16 @@
           <t>0174516672-628-725219675485</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DIFFERIN 0.1% GEL</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>DIFFERIN 0.1% GEL detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -1806,8 +1854,16 @@
           <t>8080455523-667-040451051990</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DIFFERIN 0.1% CREAM</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>DIFFERIN 0.1% CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -1997,8 +2053,16 @@
           <t>8661557618-336-585257825130</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DICLOGESIC</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>DICLOGESIC detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -2180,8 +2244,16 @@
           <t>0953290167-546-477008521915</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DURACAN 150MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>DURACAN 150MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
@@ -2363,8 +2435,16 @@
           <t>1113245442-132-921286085069</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DOXYCIN</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>DOXYCIN detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -2546,8 +2626,16 @@
           <t>9399835567-534-964136776386</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FERRIPROX 100MG/ML ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>FERRIPROX 100MG/ML ORAL SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
@@ -2725,8 +2813,16 @@
           <t>6384150678-146-758635977916</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FENAM 50MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>FENAM 50MG-5ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -2908,8 +3004,16 @@
           <t>8411581188-705-182233281855</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FLUDREX SYRUP</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>FLUDREX SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
@@ -3091,8 +3195,16 @@
           <t>0434160755-286-947493191015</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ENTAPRO 20MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>ENTAPRO 20MG FILM COATED TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>DAMMAM PHARMA</t>
@@ -3276,8 +3388,16 @@
           <t>6232334707-882-691342349104</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ENTAPRO 10MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>ENTAPRO 10MG FILM COATED TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>DAMMAM PHARMA</t>
@@ -3457,8 +3577,16 @@
           <t>2526204650-842-415798704724</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ENEMACORT 0.02MG-ML TABLET FOR ENEMA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>ENEMACORT 0.02MG-ML TABLET FOR ENEMA detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
@@ -3640,8 +3768,16 @@
           <t>2545684244-972-357191620200</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ELIDEL 1% CREAM</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ELIDEL 1% CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
@@ -3827,8 +3963,16 @@
           <t>8164381927-214-632640123177</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EMIDOL 500MG TABLET</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>EMIDOL 500MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
@@ -4022,8 +4166,16 @@
           <t>1270439117-543-842437747328</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EMILOK 20MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>EMILOK 20MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -4213,8 +4365,16 @@
           <t>9209906624-310-800171527653</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EZOLVIN 8MGTAB</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>EZOLVIN 8MGTAB detailed description.</t>
+        </is>
+      </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
@@ -4400,8 +4560,16 @@
           <t>7106443700-384-066985843991</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EZILAX 10G-15ML SYRUP</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>EZILAX 10G-15ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
@@ -4587,8 +4755,16 @@
           <t>9196330988-972-882257306836</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARXIA 60MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>ARXIA 60MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
@@ -4770,8 +4946,16 @@
           <t>0060100430-009-120809797825</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARXIA 120MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>ARXIA 120MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
@@ -4953,8 +5137,16 @@
           <t>1123636416-707-514025449668</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ROXARDIO 20MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>ROXARDIO 20MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
@@ -5136,8 +5328,16 @@
           <t>2044471141-338-778962175816</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ROXARDIO 10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>ROXARDIO 10MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
@@ -5327,8 +5527,16 @@
           <t>1507743310-612-375316496682</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VERCANZA 450 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>VERCANZA 450 MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
@@ -5510,8 +5718,16 @@
           <t>6490142173-958-783591213614</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Fostimon 300 I.U</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Fostimon 300 I.U detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
@@ -5701,8 +5917,16 @@
           <t>7392261169-346-793626023302</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SENERGY 10 MG/160 MG F.C. TABLET</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>SENERGY 10 MG/160 MG F.C. TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t xml:space="preserve">MS Pharma Saudi </t>
@@ -5890,8 +6114,16 @@
           <t>7225883607-123-619439892955</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SENERGY 5 MG/160 MG F.C. TABLET</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>SENERGY 5 MG/160 MG F.C. TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t xml:space="preserve">MS Pharma Saudi </t>
@@ -6079,8 +6311,16 @@
           <t>9264803870-676-711121208458</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLERAN 15MG TABLET</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>GLERAN 15MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
@@ -6266,8 +6506,16 @@
           <t>0411038085-871-391630755025</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLERAN 30MG TABLET</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>GLERAN 30MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -6449,8 +6697,16 @@
           <t>2468514530-393-080027301593</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OROTIX 90MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>OROTIX 90MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
@@ -6640,8 +6896,16 @@
           <t>6223698100-180-784491837090</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ JULMENTIN FORTE 312.5MG POWDER FOR SUSP</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>JULMENTIN FORTE 312.5MG POWDER FOR SUSP detailed description.</t>
+        </is>
+      </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
@@ -6827,8 +7091,16 @@
           <t>8350263281-706-375354944022</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ JULMENTIN 2X. 457MG-5ML ORAL SUSPENSION</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>JULMENTIN 2X. 457MG-5ML ORAL SUSPENSION detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -7006,8 +7278,16 @@
           <t>6027654327-696-674128358030</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DICLOGESIC RETARD</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>DICLOGESIC RETARD detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
@@ -7189,8 +7469,16 @@
           <t>2649273137-595-317999375921</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DURADOX 100 MG CAPS</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>DURADOX 100 MG CAPS detailed description.</t>
+        </is>
+      </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
@@ -7376,8 +7664,16 @@
           <t>9679766126-202-873675367912</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLAMYCIN 500 MG TABLET</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>CLAMYCIN 500 MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
@@ -7563,8 +7859,16 @@
           <t>9272224357-369-491647292149</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLOFEN CREAMAGEL 1%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>CLOFEN CREAMAGEL 1% detailed description.</t>
+        </is>
+      </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
@@ -7754,8 +8058,16 @@
           <t>5273619105-899-005562505700</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FUSIX 40MG TABLET</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>FUSIX 40MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
@@ -7941,8 +8253,16 @@
           <t>2535470371-320-828688529852</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CHLOROHISTOL TAB 4 MG.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>CHLOROHISTOL TAB 4 MG. detailed description.</t>
+        </is>
+      </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
@@ -8128,8 +8448,16 @@
           <t>8419691619-502-420392657945</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SOOLAN SYRUP 100 ML.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>SOOLAN SYRUP 100 ML. detailed description.</t>
+        </is>
+      </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
@@ -8315,8 +8643,16 @@
           <t>8999639806-850-475152481607</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARXIA 90MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>ARXIA 90MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
@@ -8498,8 +8834,16 @@
           <t>6916035679-110-542937649586</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AMLOPHAR 5MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>AMLOPHAR 5MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
@@ -8681,8 +9025,16 @@
           <t>4890264370-765-605297957949</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ 3V TABLETS</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>3V TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
@@ -8860,8 +9212,16 @@
           <t>8474251062-203-787767390232</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BEPANTHEN</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>BEPANTHEN detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
@@ -9047,8 +9407,16 @@
           <t>0371172238-491-136013467276</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ALOPEXY 5% topical solution</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>ALOPEXY 5% topical solution detailed description.</t>
+        </is>
+      </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
@@ -9230,8 +9598,16 @@
           <t>6349182162-611-465232603036</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ALOPEXY 5% topical solution</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>ALOPEXY 5% topical solution detailed description.</t>
+        </is>
+      </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
@@ -9417,8 +9793,16 @@
           <t>9629131146-672-067335476582</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TYKERB 250MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>TYKERB 250MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
@@ -9604,8 +9988,16 @@
           <t>7981757462-786-109484109413</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ KEPPRA 1000MG F.C.TAB</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>KEPPRA 1000MG F.C.TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
@@ -9791,8 +10183,16 @@
           <t>7748632793-612-467182322282</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ KEPPRA 100MG-ML ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>KEPPRA 100MG-ML ORAL SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>GLAXO SAUDI ARABIA</t>
@@ -9976,8 +10376,16 @@
           <t>7344865927-308-693108455076</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PROTOPIC 0.03% OINTMENT</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>PROTOPIC 0.03% OINTMENT detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
@@ -10163,8 +10571,16 @@
           <t>5812345827-132-013501379055</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ KEPPRA 250MG F.C.TAB</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>KEPPRA 250MG F.C.TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
           <t>GLAXO SAUDI ARABIA</t>
@@ -10352,8 +10768,16 @@
           <t>6906801805-326-424599195352</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ KEPPRA 500MG F.C.TAB</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>KEPPRA 500MG F.C.TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
           <t>GLAXO SAUDI ARABIA</t>
@@ -10533,8 +10957,16 @@
           <t>8219818230-507-319722344300</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ACUVAIL ophthalmic solution</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>ACUVAIL ophthalmic solution detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
@@ -10716,8 +11148,16 @@
           <t>6641176520-914-267168732731</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AVOQUIN cream</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>AVOQUIN cream detailed description.</t>
+        </is>
+      </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
@@ -10899,8 +11339,16 @@
           <t>2030344917-826-527576976702</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BRONCAST 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>BRONCAST 10 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
@@ -11086,8 +11534,16 @@
           <t>6392694517-911-914606177627</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BRONCAST 5 mg chewable tablet</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>BRONCAST 5 mg chewable tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -11273,8 +11729,16 @@
           <t>5986700315-311-329056261683</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZYMAXID 0.5% eye drops solution</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>ZYMAXID 0.5% eye drops solution detailed description.</t>
+        </is>
+      </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
@@ -11456,8 +11920,16 @@
           <t>2857647201-716-021045585769</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CATAFLAM 50MG TABLET</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>CATAFLAM 50MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
         <is>
           <t>SAJA-SAUDI ARABIAN JAPANESE PHARMACEUTICAL CO</t>
@@ -11645,8 +12117,16 @@
           <t>0807519271-581-932579022510</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LESCOL XL 80 MG FILM COATED TAB</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>LESCOL XL 80 MG FILM COATED TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -11828,8 +12308,16 @@
           <t>3137052372-409-150695806841</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEPAKINE 57.64MG-ML SYRUP</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>DEPAKINE 57.64MG-ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr">
         <is>
           <t>Sanofi Aventis Arabia</t>
@@ -12013,8 +12501,16 @@
           <t>8768590006-869-424503289652</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VIRECTIL 50 mg tablet</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>VIRECTIL 50 mg tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
@@ -12200,8 +12696,16 @@
           <t>0890453166-924-021379351296</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ KEMADRIN 5MG TABLET</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>KEMADRIN 5MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
@@ -12383,8 +12887,16 @@
           <t>1533007767-133-453513984558</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AKYNZEO 300 mg/0.5 mg hard capsules</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>AKYNZEO 300 mg/0.5 mg hard capsules detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
@@ -12566,8 +13078,16 @@
           <t>5788001187-475-175115316078</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AZYN 500 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>AZYN 500 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -12940,8 +13460,16 @@
           <t>6745738088-876-836397227868</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ORGALUTRAN 0.25MG\0.5ML SYRINGE</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>ORGALUTRAN 0.25MG\0.5ML SYRINGE detailed description.</t>
+        </is>
+      </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
@@ -13127,8 +13655,16 @@
           <t>0691369766-777-858587498997</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PANADOL COLD &amp; FLU VAPOUR RELEASE + DECONGESTANT  600 MG ORAL S</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>PANADOL COLD &amp; FLU VAPOUR RELEASE + DECONGESTANT  600 MG ORAL S detailed description.</t>
+        </is>
+      </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
@@ -13314,8 +13850,16 @@
           <t>3701892264-390-813305467210</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HEMLIBRA 150 MG/ML SOLUTION FOR INJECTION</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>HEMLIBRA 150 MG/ML SOLUTION FOR INJECTION detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -13505,8 +14049,16 @@
           <t>8944713579-849-381376570923</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HEMLIBRA 150 MG/ML SOLUTION FOR INJECTION</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>HEMLIBRA 150 MG/ML SOLUTION FOR INJECTION detailed description.</t>
+        </is>
+      </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
@@ -13692,8 +14244,16 @@
           <t>5514773995-499-781442353058</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HEMLIBRA 150 MG/ML SOLUTION FOR INJECTION</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>HEMLIBRA 150 MG/ML SOLUTION FOR INJECTION detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
@@ -13879,8 +14439,16 @@
           <t>5404682285-241-634341704595</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HEMLIBRA 30 MG/ML SOLUTION FOR INJECTION</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>HEMLIBRA 30 MG/ML SOLUTION FOR INJECTION detailed description.</t>
+        </is>
+      </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
@@ -14070,8 +14638,16 @@
           <t>4270353187-126-573731299891</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARCOXIA 60MG TAB</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>ARCOXIA 60MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
@@ -14253,8 +14829,16 @@
           <t>9630046136-738-287878857732</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARCOXIA 90MG TAB</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>ARCOXIA 90MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
@@ -14436,8 +15020,16 @@
           <t>2911697988-157-041688066327</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CARPAZIO 600 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>CARPAZIO 600 MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
@@ -14623,8 +15215,16 @@
           <t>4995633055-396-769014764774</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Arkator 60MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Arkator 60MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
@@ -14810,8 +15410,16 @@
           <t>6365262467-553-859116989437</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Arkator 90MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Arkator 90MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
@@ -14993,8 +15601,16 @@
           <t>2873604210-144-823237184873</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Arkator 120MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Arkator 120MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
@@ -15176,8 +15792,16 @@
           <t>5234293929-959-123598097957</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PLATEREL 5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>PLATEREL 5MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
@@ -15363,8 +15987,16 @@
           <t>8496112165-290-857334943032</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PLATEREL 10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>PLATEREL 10MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
@@ -15550,8 +16182,16 @@
           <t>0448578302-346-145493428389</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZAHRA TABLET</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>ZAHRA TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
@@ -15737,8 +16377,16 @@
           <t>6892556516-699-252590823034</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MONTAS 4 mg Chewable Tablets</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>MONTAS 4 mg Chewable Tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
@@ -15920,8 +16568,16 @@
           <t>1191396939-549-536091383962</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MONTAS 5 mg Chewable Tablets</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>MONTAS 5 mg Chewable Tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -16103,8 +16759,16 @@
           <t>1447253147-261-043273245163</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZYTERO 12.5 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>ZYTERO 12.5 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
@@ -16290,8 +16954,16 @@
           <t>5441983443-482-869668318429</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZYTERO 25 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>ZYTERO 25 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
@@ -16473,8 +17145,16 @@
           <t>8209183066-430-714743636663</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OXIRA 8MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>OXIRA 8MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -16656,8 +17336,16 @@
           <t>4521455386-999-384212533039</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MARLET 2.5 MG F.C. TABLET</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>MARLET 2.5 MG F.C. TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -16843,8 +17531,16 @@
           <t>7299157895-598-847964021251</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ALDACTONE TAB</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>ALDACTONE TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
@@ -17030,8 +17726,16 @@
           <t>4377182474-143-444498418511</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZYLORIC 100MG TABLET</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>ZYLORIC 100MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
           <t>DEEF PHARMACEUTICAL INDUSTRIES</t>
@@ -17219,8 +17923,16 @@
           <t>3070862673-342-169773122588</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MAXITROL</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>MAXITROL detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
@@ -17402,8 +18114,16 @@
           <t>1497008361-949-986442078860</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SALAZOPYRIN-EN TAB 500MG</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>SALAZOPYRIN-EN TAB 500MG detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
@@ -17593,8 +18313,16 @@
           <t>9394452308-746-792485475255</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LIVADOR 750MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>LIVADOR 750MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
@@ -17780,8 +18508,16 @@
           <t>9905132709-367-296121936232</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ENNLA 5% Cream</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>ENNLA 5% Cream detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
@@ -17967,8 +18703,16 @@
           <t>6428128248-034-996210781506</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TRELEGY ELLIPTA 100/62.5/25MCG Inhalation powder, pre-dispensed</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>TRELEGY ELLIPTA 100/62.5/25MCG Inhalation powder, pre-dispensed detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
@@ -18154,8 +18898,16 @@
           <t>6077250156-970-315556603634</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GAMCET 0.4MG PROLONGED RELEASE F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>GAMCET 0.4MG PROLONGED RELEASE F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
@@ -18337,8 +19089,16 @@
           <t>6272542585-066-798660509495</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LIVADOR 500 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>LIVADOR 500 MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
@@ -18516,8 +19276,16 @@
           <t>2585280235-692-844291495788</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Xevaneer 300 mg capsule</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Xevaneer 300 mg capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
@@ -18703,8 +19471,16 @@
           <t>6436726037-737-436081831596</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ XEVANEER 125mg/5ml Powder For Oral Suspension</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>XEVANEER 125mg/5ml Powder For Oral Suspension detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
@@ -18882,8 +19658,16 @@
           <t>8854628120-575-056971047235</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ WELLBUTRIN XL 150 EXTENDED RELEASE F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>WELLBUTRIN XL 150 EXTENDED RELEASE F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
@@ -19069,8 +19853,16 @@
           <t>5531631491-994-819488606850</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DESCOVY 200MG/25MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>DESCOVY 200MG/25MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/63/file.xlsx
+++ b/product_upload/packages/63/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20078,7 +20078,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -21700,7 +21700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21781,40 +21781,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -21894,38 +21899,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>143.52</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-A3C1CA424BF6</t>
         </is>
@@ -22005,38 +22015,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>336.69</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-BDE142D751B0</t>
         </is>
@@ -22116,38 +22131,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>250.02</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-8E5708240C03</t>
         </is>
@@ -22227,38 +22247,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>144.83</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-8AAB06A15BDD</t>
         </is>
@@ -22338,38 +22363,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>88.83</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-E88C87B53CAD</t>
         </is>
@@ -22449,38 +22479,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>339.22</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-6AD9719DF639</t>
         </is>
@@ -22560,38 +22595,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>139.52</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-085CCACE540D</t>
         </is>
@@ -22671,38 +22711,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>22.43</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-74F8B570D4C7</t>
         </is>
@@ -22782,38 +22827,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>489.47</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-418C2499FB3C</t>
         </is>
@@ -22893,38 +22943,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>393.15</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-44C6E95AD56F</t>
         </is>
@@ -23004,38 +23059,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>323.96</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-B37551A70701</t>
         </is>
@@ -23115,38 +23175,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>97.45999999999999</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-F7DB23981B87</t>
         </is>
@@ -23226,38 +23291,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>153.9</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-FB0EB12F438D</t>
         </is>
@@ -23337,38 +23407,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>130.84</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-65B6EBCAC1BA</t>
         </is>
@@ -23448,38 +23523,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>478.44</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-D92D67ED716A</t>
         </is>
@@ -23559,38 +23639,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>63.25</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-9686B665F795</t>
         </is>
@@ -23670,38 +23755,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>384.63</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-265B780FEAEE</t>
         </is>
@@ -23781,38 +23871,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>302.61</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-CD82054B1359</t>
         </is>
@@ -23892,38 +23987,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>36.47</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-CC43076894E6</t>
         </is>
@@ -24003,38 +24103,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>443.69</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-57502B855315</t>
         </is>
